--- a/research/traditional_assets/database/data/philippines/philippines_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,109 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05280000000000001</v>
-      </c>
-      <c r="E2">
-        <v>0.164</v>
+        <v>0.171</v>
       </c>
       <c r="G2">
-        <v>0.003277674706246134</v>
+        <v>0.03492307692307692</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.02876923076923077</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-0.04261538461538462</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-0.03520998343111691</v>
       </c>
       <c r="K2">
-        <v>11.86</v>
+        <v>1.262</v>
       </c>
       <c r="L2">
-        <v>0.3667285095856524</v>
+        <v>0.1941538461538461</v>
       </c>
       <c r="M2">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.00467454134204574</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.1568296795952783</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.00467454134204574</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.1568296795952783</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>68.28</v>
+        <v>12.813</v>
       </c>
       <c r="V2">
-        <v>0.1716009047499372</v>
+        <v>0.09090457609081236</v>
       </c>
       <c r="W2">
-        <v>0.1092686604674541</v>
+        <v>0.01904411764705883</v>
       </c>
       <c r="X2">
-        <v>0.1108097275975865</v>
+        <v>0.08079874009356669</v>
       </c>
       <c r="Y2">
-        <v>-0.001541067130132384</v>
+        <v>-0.06175462244650787</v>
       </c>
       <c r="Z2">
-        <v>1.540586890243903</v>
+        <v>0.05369105341846807</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04383172847575457</v>
+        <v>0.08079306316108037</v>
       </c>
       <c r="AC2">
-        <v>-0.04383172847575457</v>
+        <v>-0.09169499140022574</v>
       </c>
       <c r="AD2">
-        <v>106.339</v>
+        <v>105.135</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>106.339</v>
+        <v>105.135</v>
       </c>
       <c r="AG2">
-        <v>38.059</v>
+        <v>92.32199999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2108900739530262</v>
+        <v>0.427230428510474</v>
       </c>
       <c r="AI2">
-        <v>0.6591028827499861</v>
+        <v>0.6503182467665015</v>
       </c>
       <c r="AJ2">
-        <v>0.08729949375973427</v>
+        <v>0.3957697451901642</v>
       </c>
       <c r="AK2">
-        <v>0.408977100549114</v>
+        <v>0.6202184691039542</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.006</v>
+      </c>
+      <c r="AN2">
+        <v>-443.6075949367088</v>
+      </c>
+      <c r="AO2">
+        <v>-46.16666666666667</v>
+      </c>
+      <c r="AP2">
+        <v>-389.5443037974683</v>
+      </c>
+      <c r="AQ2">
+        <v>-46.16666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COL Financial Group, Inc. (PSE:COL)</t>
+          <t>Medco Holdings, Inc. (PSE:MED)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,104 +715,80 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.123</v>
-      </c>
-      <c r="E3">
-        <v>0.164</v>
-      </c>
-      <c r="G3">
-        <v>0.003745583038869258</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>0.4946996466431095</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="M3">
-        <v>1.86</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.004848800834202294</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1328571428571429</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.86</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.004848800834202294</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1328571428571429</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>65.2</v>
+        <v>0.133</v>
       </c>
       <c r="V3">
-        <v>0.1699687174139729</v>
+        <v>0.01437837837837838</v>
       </c>
       <c r="W3">
-        <v>0.4046242774566474</v>
+        <v>-0.1300448430493273</v>
       </c>
       <c r="X3">
-        <v>0.04185357091711564</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="Y3">
-        <v>0.3627707065395317</v>
+        <v>-0.2108342816849684</v>
       </c>
       <c r="Z3">
-        <v>-0.3659640501745764</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04182969291344641</v>
+        <v>0.08078943863564109</v>
       </c>
       <c r="AC3">
-        <v>-0.04182969291344641</v>
+        <v>-0.08078943863564109</v>
       </c>
       <c r="AD3">
-        <v>0.839</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.839</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-64.361</v>
+        <v>-0.133</v>
       </c>
       <c r="AH3">
-        <v>0.002182400849029365</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.019863159639196</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2016075730095634</v>
+        <v>-0.01458813206098497</v>
       </c>
       <c r="AK3">
-        <v>2.803057358129001</v>
+        <v>-0.3333333333333333</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +814,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0174</v>
+        <v>0.171</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -847,10 +829,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-2.14</v>
+        <v>0.259</v>
       </c>
       <c r="L4">
-        <v>-0.5297029702970297</v>
+        <v>0.0505859375</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -859,7 +841,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -868,67 +850,192 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.08</v>
+        <v>1.38</v>
       </c>
       <c r="V4">
-        <v>0.2153846153846154</v>
+        <v>0.1045454545454545</v>
       </c>
       <c r="W4">
-        <v>-0.1860869565217391</v>
+        <v>0.01904411764705883</v>
       </c>
       <c r="X4">
-        <v>0.1797658842780573</v>
+        <v>0.3315331886700659</v>
       </c>
       <c r="Y4">
-        <v>-0.3658528407997965</v>
+        <v>-0.3124890710230071</v>
       </c>
       <c r="Z4">
-        <v>0.04108948149956266</v>
+        <v>0.04439511653718091</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04583376403806273</v>
+        <v>0.09169499140022574</v>
       </c>
       <c r="AC4">
-        <v>-0.04583376403806273</v>
+        <v>-0.09169499140022574</v>
       </c>
       <c r="AD4">
-        <v>105.5</v>
+        <v>105.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>105.5</v>
+        <v>105.1</v>
       </c>
       <c r="AG4">
-        <v>102.42</v>
+        <v>103.72</v>
       </c>
       <c r="AH4">
-        <v>0.8806343906510852</v>
+        <v>0.8884192730346576</v>
       </c>
       <c r="AI4">
-        <v>0.8858102434928632</v>
+        <v>0.829518547750592</v>
       </c>
       <c r="AJ4">
-        <v>0.8774845784784099</v>
+        <v>0.8871022921655832</v>
       </c>
       <c r="AK4">
-        <v>0.8827788312359939</v>
+        <v>0.8276412384296202</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CTS Global Equity Group, Inc. (PSE:CTS)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0.1644927536231884</v>
+      </c>
+      <c r="H5">
+        <v>0.1355072463768116</v>
+      </c>
+      <c r="I5">
+        <v>-0.2007246376811594</v>
+      </c>
+      <c r="J5">
+        <v>-0.1709295742753623</v>
+      </c>
+      <c r="K5">
+        <v>1.09</v>
+      </c>
+      <c r="L5">
+        <v>0.7898550724637682</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>11.3</v>
+      </c>
+      <c r="V5">
+        <v>0.09535864978902954</v>
+      </c>
+      <c r="W5">
+        <v>0.09396551724137932</v>
+      </c>
+      <c r="X5">
+        <v>0.08079874009356669</v>
+      </c>
+      <c r="Y5">
+        <v>0.01316677714781263</v>
+      </c>
+      <c r="Z5">
+        <v>0.2658959537572254</v>
+      </c>
+      <c r="AA5">
+        <v>-0.04544948217726397</v>
+      </c>
+      <c r="AB5">
+        <v>0.08079306316108037</v>
+      </c>
+      <c r="AC5">
+        <v>-0.1262425453383443</v>
+      </c>
+      <c r="AD5">
+        <v>0.035</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0.035</v>
+      </c>
+      <c r="AG5">
+        <v>-11.265</v>
+      </c>
+      <c r="AH5">
+        <v>0.0002952714388155397</v>
+      </c>
+      <c r="AI5">
+        <v>0.001016407724698708</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1050496572947265</v>
+      </c>
+      <c r="AK5">
+        <v>-0.4869245731575536</v>
+      </c>
+      <c r="AL5">
+        <v>0.006</v>
+      </c>
+      <c r="AM5">
+        <v>0.006</v>
+      </c>
+      <c r="AN5">
+        <v>-0.1476793248945148</v>
+      </c>
+      <c r="AO5">
+        <v>-46.16666666666667</v>
+      </c>
+      <c r="AP5">
+        <v>47.53164556962026</v>
+      </c>
+      <c r="AQ5">
+        <v>-46.16666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/philippines/philippines_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_brokerage_investment_banking.xlsx
@@ -588,115 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.171</v>
+        <v>-0.6709999999999999</v>
       </c>
       <c r="G2">
-        <v>0.03492307692307692</v>
+        <v>-0.1341772151898734</v>
       </c>
       <c r="H2">
-        <v>0.02876923076923077</v>
+        <v>-0.1632911392405063</v>
       </c>
       <c r="I2">
-        <v>-0.04261538461538462</v>
+        <v>-0.130379746835443</v>
       </c>
       <c r="J2">
-        <v>-0.03520998343111691</v>
+        <v>-0.130379746835443</v>
       </c>
       <c r="K2">
-        <v>1.262</v>
+        <v>-6.802</v>
       </c>
       <c r="L2">
-        <v>0.1941538461538461</v>
+        <v>-4.30506329113924</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0008597823104362938</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0.01381946486327551</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0008597823104362938</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0.01381946486327551</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>12.813</v>
+        <v>16.984</v>
       </c>
       <c r="V2">
-        <v>0.09090457609081236</v>
+        <v>0.1553461995792555</v>
       </c>
       <c r="W2">
-        <v>0.01904411764705883</v>
+        <v>-0.1860902255639098</v>
       </c>
       <c r="X2">
-        <v>0.08079874009356669</v>
+        <v>0.06881402558169591</v>
       </c>
       <c r="Y2">
-        <v>-0.06175462244650787</v>
+        <v>-0.2549042511456057</v>
       </c>
       <c r="Z2">
-        <v>0.05369105341846807</v>
+        <v>0.01065752907212045</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.08079306316108037</v>
+        <v>0.06799667284010258</v>
       </c>
       <c r="AC2">
-        <v>-0.09169499140022574</v>
+        <v>-0.07625316123454172</v>
       </c>
       <c r="AD2">
-        <v>105.135</v>
+        <v>111.115</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>105.135</v>
+        <v>111.115</v>
       </c>
       <c r="AG2">
-        <v>92.32199999999999</v>
+        <v>94.131</v>
       </c>
       <c r="AH2">
-        <v>0.427230428510474</v>
+        <v>0.5040486289097055</v>
       </c>
       <c r="AI2">
-        <v>0.6503182467665015</v>
+        <v>0.674831163152269</v>
       </c>
       <c r="AJ2">
-        <v>0.3957697451901642</v>
+        <v>0.4626488614525633</v>
       </c>
       <c r="AK2">
-        <v>0.6202184691039542</v>
+        <v>0.6374329595319357</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AM2">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AN2">
-        <v>-443.6075949367088</v>
+        <v>-673.4242424242425</v>
       </c>
       <c r="AO2">
-        <v>-46.16666666666667</v>
+        <v>-11.44444444444444</v>
       </c>
       <c r="AP2">
-        <v>-389.5443037974683</v>
+        <v>-570.4909090909091</v>
       </c>
       <c r="AQ2">
-        <v>-46.16666666666667</v>
+        <v>-11.44444444444444</v>
       </c>
     </row>
     <row r="3">
@@ -715,8 +718,11 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>-0.6709999999999999</v>
+      </c>
       <c r="K3">
-        <v>-0.08699999999999999</v>
+        <v>-0.099</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,19 +746,19 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.133</v>
+        <v>0.134</v>
       </c>
       <c r="V3">
-        <v>0.01437837837837838</v>
+        <v>0.02612085769980507</v>
       </c>
       <c r="W3">
-        <v>-0.1300448430493273</v>
+        <v>-0.1860902255639098</v>
       </c>
       <c r="X3">
-        <v>0.08078943863564109</v>
+        <v>0.06881402558169591</v>
       </c>
       <c r="Y3">
-        <v>-0.2108342816849684</v>
+        <v>-0.2549042511456057</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -761,34 +767,34 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.08078943863564109</v>
+        <v>0.06799667284010258</v>
       </c>
       <c r="AC3">
-        <v>-0.08078943863564109</v>
+        <v>-0.06799667284010258</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.341</v>
       </c>
       <c r="AG3">
-        <v>-0.133</v>
+        <v>0.207</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.0623286419301773</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.3866213151927437</v>
       </c>
       <c r="AJ3">
-        <v>-0.01458813206098497</v>
+        <v>0.03878583473861721</v>
       </c>
       <c r="AK3">
-        <v>-0.3333333333333333</v>
+        <v>0.2767379679144386</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -813,26 +819,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.171</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
       <c r="K4">
-        <v>0.259</v>
-      </c>
-      <c r="L4">
-        <v>0.0505859375</v>
+        <v>-6.69</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -841,7 +829,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -850,61 +838,61 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.38</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V4">
-        <v>0.1045454545454545</v>
+        <v>0.8378378378378379</v>
       </c>
       <c r="W4">
-        <v>0.01904411764705883</v>
+        <v>-0.3097222222222222</v>
       </c>
       <c r="X4">
-        <v>0.3315331886700659</v>
+        <v>0.281225016464614</v>
       </c>
       <c r="Y4">
-        <v>-0.3124890710230071</v>
+        <v>-0.5909472386868362</v>
       </c>
       <c r="Z4">
-        <v>0.04439511653718091</v>
+        <v>0</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09169499140022574</v>
+        <v>0.07625316123454172</v>
       </c>
       <c r="AC4">
-        <v>-0.09169499140022574</v>
+        <v>-0.07625316123454172</v>
       </c>
       <c r="AD4">
-        <v>105.1</v>
+        <v>110.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>105.1</v>
+        <v>110.7</v>
       </c>
       <c r="AG4">
-        <v>103.72</v>
+        <v>101.4</v>
       </c>
       <c r="AH4">
-        <v>0.8884192730346576</v>
+        <v>0.9088669950738917</v>
       </c>
       <c r="AI4">
-        <v>0.829518547750592</v>
+        <v>0.8621495327102804</v>
       </c>
       <c r="AJ4">
-        <v>0.8871022921655832</v>
+        <v>0.9013333333333334</v>
       </c>
       <c r="AK4">
-        <v>0.8276412384296202</v>
+        <v>0.8513853904282116</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -930,112 +918,115 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.1644927536231884</v>
+        <v>-0.1341772151898734</v>
       </c>
       <c r="H5">
-        <v>0.1355072463768116</v>
+        <v>-0.1632911392405063</v>
       </c>
       <c r="I5">
-        <v>-0.2007246376811594</v>
+        <v>-0.130379746835443</v>
       </c>
       <c r="J5">
-        <v>-0.1709295742753623</v>
+        <v>-0.130379746835443</v>
       </c>
       <c r="K5">
-        <v>1.09</v>
+        <v>-0.013</v>
       </c>
       <c r="L5">
-        <v>0.7898550724637682</v>
+        <v>-0.008227848101265822</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.094</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.001009667024704619</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>-7.230769230769231</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.094</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.001009667024704619</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>-7.230769230769231</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>11.3</v>
+        <v>7.55</v>
       </c>
       <c r="V5">
-        <v>0.09535864978902954</v>
+        <v>0.08109559613319012</v>
       </c>
       <c r="W5">
-        <v>0.09396551724137932</v>
+        <v>-0.000377906976744186</v>
       </c>
       <c r="X5">
-        <v>0.08079874009356669</v>
+        <v>0.0674058095946856</v>
       </c>
       <c r="Y5">
-        <v>0.01316677714781263</v>
+        <v>-0.06778371657142979</v>
       </c>
       <c r="Z5">
-        <v>0.2658959537572254</v>
+        <v>0.06829479144153881</v>
       </c>
       <c r="AA5">
-        <v>-0.04544948217726397</v>
+        <v>-0.008904257618327211</v>
       </c>
       <c r="AB5">
-        <v>0.08079306316108037</v>
+        <v>0.0673914612383411</v>
       </c>
       <c r="AC5">
-        <v>-0.1262425453383443</v>
+        <v>-0.0762957188566683</v>
       </c>
       <c r="AD5">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.035</v>
+        <v>0.074</v>
       </c>
       <c r="AG5">
-        <v>-11.265</v>
+        <v>-7.476</v>
       </c>
       <c r="AH5">
-        <v>0.0002952714388155397</v>
+        <v>0.0007942129778693627</v>
       </c>
       <c r="AI5">
-        <v>0.001016407724698708</v>
+        <v>0.002091931927404308</v>
       </c>
       <c r="AJ5">
-        <v>-0.1050496572947265</v>
+        <v>-0.08731196860693265</v>
       </c>
       <c r="AK5">
-        <v>-0.4869245731575536</v>
+        <v>-0.2686889016676251</v>
       </c>
       <c r="AL5">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AM5">
-        <v>0.006</v>
+        <v>0.018</v>
       </c>
       <c r="AN5">
-        <v>-0.1476793248945148</v>
+        <v>-0.4484848484848484</v>
       </c>
       <c r="AO5">
-        <v>-46.16666666666667</v>
+        <v>-11.44444444444444</v>
       </c>
       <c r="AP5">
-        <v>47.53164556962026</v>
+        <v>45.30909090909091</v>
       </c>
       <c r="AQ5">
-        <v>-46.16666666666667</v>
+        <v>-11.44444444444444</v>
       </c>
     </row>
   </sheetData>
